--- a/workspace/framework_paper/edf-local/gradient_edf_local_eval/gradient_edf_local_eval_times_success.xlsx
+++ b/workspace/framework_paper/edf-local/gradient_edf_local_eval/gradient_edf_local_eval_times_success.xlsx
@@ -438,13 +438,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00654482999118045</v>
+        <v>0.004564100014977157</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01580850569531321</v>
+        <v>0.007609884152188897</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6616600349918008</v>
+        <v>0.1115532325953245</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.007260955045931041</v>
+        <v>0.005662849994841963</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01658278334885836</v>
+        <v>0.01002910828217864</v>
       </c>
       <c r="D3" t="n">
-        <v>1.035451195975766</v>
+        <v>0.1842667858023196</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.008058335881214589</v>
+        <v>0.005380057520233095</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01667806915938854</v>
+        <v>0.008796475082635879</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9146542728226632</v>
+        <v>0.3718120485451072</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.008884774171747267</v>
+        <v>0.005700645716860891</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02236485004425049</v>
+        <v>0.01061900837346911</v>
       </c>
       <c r="D5" t="n">
-        <v>1.353683497849852</v>
+        <v>0.4049730947148055</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01290937319863588</v>
+        <v>0.00590958240441978</v>
       </c>
       <c r="C6" t="n">
-        <v>0.03293123073875904</v>
+        <v>0.01196313916705549</v>
       </c>
       <c r="D6" t="n">
-        <v>1.970774980951101</v>
+        <v>0.4856099664699286</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01120525745209306</v>
+        <v>0.006926872553303837</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03090339239686728</v>
+        <v>0.01409203078597784</v>
       </c>
       <c r="D7" t="n">
-        <v>3.544886353672767</v>
+        <v>0.7823421575687826</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.01360991745605133</v>
+        <v>0.00777387319311024</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04742664260295581</v>
+        <v>0.04298760854639113</v>
       </c>
       <c r="D8" t="n">
-        <v>4.931009548051017</v>
+        <v>1.167409283984453</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01440387683333424</v>
+        <v>0.01068769294120695</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0618103135909353</v>
+        <v>0.05382825850509107</v>
       </c>
       <c r="D9" t="n">
-        <v>2.904796898365021</v>
+        <v>1.419340071603656</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0164253296641012</v>
+        <v>0.009722219753629443</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1157901741906392</v>
+        <v>0.0330009202910017</v>
       </c>
       <c r="D10" t="n">
-        <v>4.958750231191516</v>
+        <v>2.162894612737</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01949134275782853</v>
+        <v>0.01519491176965625</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1424454719273616</v>
+        <v>0.05009855163682785</v>
       </c>
       <c r="D11" t="n">
-        <v>5.52838372707367</v>
+        <v>4.187140171527862</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02356089916276304</v>
+        <v>0.01118888434721157</v>
       </c>
       <c r="C12" t="n">
-        <v>0.125213881711597</v>
+        <v>0.1232541775172378</v>
       </c>
       <c r="D12" t="n">
-        <v>6.554901414729179</v>
+        <v>25.22202500224114</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.06918110280659878</v>
+        <v>0.01612965479227049</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3015772600968679</v>
+        <v>0.3780408861242573</v>
       </c>
       <c r="D13" t="n">
-        <v>11.4709332937544</v>
+        <v>7.795535500049591</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.06822081664577126</v>
+        <v>0.01897852757776325</v>
       </c>
       <c r="C14" t="n">
-        <v>1.538847170724738</v>
+        <v>0.1649657381741806</v>
       </c>
       <c r="D14" t="n">
-        <v>15.41471037810499</v>
+        <v>9.326622211933136</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1201505412516946</v>
+        <v>0.05779978203981255</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9730197834089781</v>
+        <v>1.01319399352597</v>
       </c>
       <c r="D15" t="n">
-        <v>19.44116963310675</v>
+        <v>17.64656950565095</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.06107200385026988</v>
+        <v>0.02450128450341846</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7810211078030989</v>
+        <v>4.326014649887115</v>
       </c>
       <c r="D16" t="n">
-        <v>29.96354504329402</v>
+        <v>18.31561186313629</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0.08099791506538168</v>
+        <v>0.02423983956932237</v>
       </c>
       <c r="C17" t="n">
-        <v>1.019964676001109</v>
+        <v>1.579620180990208</v>
       </c>
       <c r="D17" t="n">
-        <v>55.04855053565081</v>
+        <v>20.50428307056427</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1318098811263388</v>
+        <v>0.03164115032324424</v>
       </c>
       <c r="C18" t="n">
-        <v>1.554870159537704</v>
+        <v>2.339121981790023</v>
       </c>
       <c r="D18" t="n">
-        <v>115.9969251232763</v>
+        <v>48.03675856957069</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0.09327800944447517</v>
+        <v>0.04358056280761957</v>
       </c>
       <c r="C19" t="n">
-        <v>7.676511908379885</v>
+        <v>1.463865990042686</v>
       </c>
       <c r="D19" t="n">
-        <v>101.1452584681304</v>
+        <v>55.97076163572424</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0.1235488057136536</v>
+        <v>0.05856547025697572</v>
       </c>
       <c r="C20" t="n">
-        <v>5.454637390375138</v>
+        <v>2.18827166667451</v>
       </c>
       <c r="D20" t="n">
-        <v>96.52008605003357</v>
+        <v>77.67140914653909</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0.1608883142471313</v>
+        <v>0.07814937581618626</v>
       </c>
       <c r="C21" t="n">
-        <v>10.47786507468957</v>
+        <v>6.800665740172068</v>
       </c>
       <c r="D21" t="n">
-        <v>211.1148172106062</v>
+        <v>81.99547677881577</v>
       </c>
     </row>
   </sheetData>
